--- a/data_lake/industry/CFM/Channel SSD.xlsx
+++ b/data_lake/industry/CFM/Channel SSD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D6F6D5-491F-42DA-B762-F3F734B7768A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5F171B-170D-6349-B3EB-2AFEEBD75AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18180" yWindow="780" windowWidth="17820" windowHeight="20700" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Channel SSD 120GB SATA" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -75,32 +75,32 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -138,54 +138,54 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -463,20 +463,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -522,7 +522,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -545,7 +545,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -568,7 +568,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -591,7 +591,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -614,7 +614,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -637,7 +637,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -660,7 +660,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -683,7 +683,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -706,7 +706,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -729,7 +729,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -752,7 +752,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -775,7 +775,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -798,7 +798,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -821,7 +821,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -844,7 +844,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -867,7 +867,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -890,7 +890,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -913,7 +913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -936,7 +936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -959,7 +959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -982,7 +982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -1692,6 +1692,167 @@
         <v>17.7</v>
       </c>
       <c r="G53" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>16</v>
+      </c>
+      <c r="F54" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G54" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>16</v>
+      </c>
+      <c r="F55" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G55" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>16</v>
+      </c>
+      <c r="F56" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G56" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>16</v>
+      </c>
+      <c r="F57" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G57" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>16</v>
+      </c>
+      <c r="F58" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G58" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>16</v>
+      </c>
+      <c r="F59" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G59" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>16</v>
+      </c>
+      <c r="F60" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G60" s="9">
         <v>17</v>
       </c>
     </row>
@@ -1703,20 +1864,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A82D123-E18C-4733-B397-9C03328A1E65}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1739,7 +1900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1762,7 +1923,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1785,7 +1946,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1808,7 +1969,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1831,7 +1992,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1854,7 +2015,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1877,7 +2038,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1900,7 +2061,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1923,7 +2084,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1946,7 +2107,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1969,7 +2130,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1992,7 +2153,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2015,7 +2176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2038,7 +2199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2061,7 +2222,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2084,7 +2245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2107,7 +2268,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2130,7 +2291,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2153,7 +2314,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2176,7 +2337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2199,7 +2360,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2222,7 +2383,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2245,7 +2406,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2268,7 +2429,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2291,7 +2452,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2314,7 +2475,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2337,7 +2498,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2360,7 +2521,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2383,7 +2544,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2406,7 +2567,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2429,7 +2590,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2452,7 +2613,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2475,7 +2636,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2498,7 +2659,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2521,7 +2682,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2544,7 +2705,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2567,7 +2728,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2590,7 +2751,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2613,7 +2774,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2636,7 +2797,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2659,7 +2820,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2682,7 +2843,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2705,7 +2866,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2728,7 +2889,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2751,7 +2912,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2774,7 +2935,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2797,7 +2958,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2820,7 +2981,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -2843,7 +3004,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -2866,7 +3027,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -2889,7 +3050,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -2912,7 +3073,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -2932,6 +3093,167 @@
         <v>37</v>
       </c>
       <c r="G53" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="12">
+        <v>34</v>
+      </c>
+      <c r="F54" s="12">
+        <v>37</v>
+      </c>
+      <c r="G54" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="12">
+        <v>34</v>
+      </c>
+      <c r="F55" s="12">
+        <v>37</v>
+      </c>
+      <c r="G55" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="12">
+        <v>34</v>
+      </c>
+      <c r="F56" s="12">
+        <v>37</v>
+      </c>
+      <c r="G56" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="12">
+        <v>34</v>
+      </c>
+      <c r="F57" s="12">
+        <v>37</v>
+      </c>
+      <c r="G57" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="12">
+        <v>34</v>
+      </c>
+      <c r="F58" s="12">
+        <v>37</v>
+      </c>
+      <c r="G58" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="12">
+        <v>34</v>
+      </c>
+      <c r="F59" s="12">
+        <v>37</v>
+      </c>
+      <c r="G59" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="12">
+        <v>34</v>
+      </c>
+      <c r="F60" s="12">
+        <v>37</v>
+      </c>
+      <c r="G60" s="12">
         <v>36</v>
       </c>
     </row>
@@ -2943,20 +3265,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DEEDA6-23E7-43DF-BF44-327B2DB18A4F}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2979,7 +3301,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3002,7 +3324,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3025,7 +3347,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3048,7 +3370,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3071,7 +3393,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3094,7 +3416,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3117,7 +3439,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3140,7 +3462,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3163,7 +3485,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3186,7 +3508,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3209,7 +3531,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3232,7 +3554,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3255,7 +3577,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3278,7 +3600,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3301,7 +3623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3324,7 +3646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3347,7 +3669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3370,7 +3692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3393,7 +3715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3416,7 +3738,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3439,7 +3761,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3462,7 +3784,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3485,7 +3807,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3508,7 +3830,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3531,7 +3853,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3554,7 +3876,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3577,7 +3899,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3600,7 +3922,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3623,7 +3945,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3646,7 +3968,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3669,7 +3991,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3692,7 +4014,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3715,7 +4037,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3738,7 +4060,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3761,7 +4083,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3784,7 +4106,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3807,7 +4129,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3830,7 +4152,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3853,7 +4175,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3876,7 +4198,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3899,7 +4221,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3922,7 +4244,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3945,7 +4267,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3968,7 +4290,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3991,7 +4313,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4014,7 +4336,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4037,7 +4359,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4060,7 +4382,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -4083,7 +4405,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -4106,7 +4428,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -4129,7 +4451,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -4152,7 +4474,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -4172,6 +4494,167 @@
         <v>66</v>
       </c>
       <c r="G53" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F54" s="9">
+        <v>66</v>
+      </c>
+      <c r="G54" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F55" s="9">
+        <v>66</v>
+      </c>
+      <c r="G55" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F56" s="9">
+        <v>66</v>
+      </c>
+      <c r="G56" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F57" s="9">
+        <v>66</v>
+      </c>
+      <c r="G57" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F58" s="9">
+        <v>66</v>
+      </c>
+      <c r="G58" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F59" s="9">
+        <v>66</v>
+      </c>
+      <c r="G59" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F60" s="9">
+        <v>66</v>
+      </c>
+      <c r="G60" s="9">
         <v>65</v>
       </c>
     </row>
@@ -4183,20 +4666,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F96F38-689A-4B46-8DFA-A4944FA7A43B}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4219,7 +4702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4242,7 +4725,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4265,7 +4748,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4288,7 +4771,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4311,7 +4794,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4334,7 +4817,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4357,7 +4840,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4380,7 +4863,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4403,7 +4886,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4426,7 +4909,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4449,7 +4932,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4472,7 +4955,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4495,7 +4978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4518,7 +5001,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4541,7 +5024,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4564,7 +5047,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4587,7 +5070,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4610,7 +5093,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4633,7 +5116,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4656,7 +5139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4679,7 +5162,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4702,7 +5185,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4725,7 +5208,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4748,7 +5231,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4771,7 +5254,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4794,7 +5277,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4817,7 +5300,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4840,7 +5323,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4863,7 +5346,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4886,7 +5369,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4909,7 +5392,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4932,7 +5415,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4955,7 +5438,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4978,7 +5461,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -5001,7 +5484,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5024,7 +5507,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5047,7 +5530,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5070,7 +5553,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5093,7 +5576,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -5116,7 +5599,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -5139,7 +5622,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -5162,7 +5645,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -5185,7 +5668,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -5208,7 +5691,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -5231,7 +5714,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -5254,7 +5737,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -5277,7 +5760,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -5300,7 +5783,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -5323,7 +5806,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -5346,7 +5829,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -5369,7 +5852,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -5392,7 +5875,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -5412,6 +5895,167 @@
         <v>39</v>
       </c>
       <c r="G53" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="14">
+        <v>37</v>
+      </c>
+      <c r="F54" s="14">
+        <v>39</v>
+      </c>
+      <c r="G54" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="14">
+        <v>37</v>
+      </c>
+      <c r="F55" s="14">
+        <v>39</v>
+      </c>
+      <c r="G55" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="14">
+        <v>37</v>
+      </c>
+      <c r="F56" s="14">
+        <v>39</v>
+      </c>
+      <c r="G56" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="14">
+        <v>37</v>
+      </c>
+      <c r="F57" s="14">
+        <v>39</v>
+      </c>
+      <c r="G57" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="14">
+        <v>37</v>
+      </c>
+      <c r="F58" s="14">
+        <v>39</v>
+      </c>
+      <c r="G58" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="14">
+        <v>37</v>
+      </c>
+      <c r="F59" s="14">
+        <v>39</v>
+      </c>
+      <c r="G59" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="14">
+        <v>37</v>
+      </c>
+      <c r="F60" s="14">
+        <v>39</v>
+      </c>
+      <c r="G60" s="14">
         <v>38</v>
       </c>
     </row>
@@ -5423,19 +6067,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAF9F8A-7AB5-472F-A579-46036402780F}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5458,7 +6102,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -5481,7 +6125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5504,7 +6148,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5527,7 +6171,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5550,7 +6194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5573,7 +6217,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5596,7 +6240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5619,7 +6263,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5642,7 +6286,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5665,7 +6309,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5688,7 +6332,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5711,7 +6355,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5734,7 +6378,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5757,7 +6401,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5780,7 +6424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5803,7 +6447,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5826,7 +6470,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5849,7 +6493,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5872,7 +6516,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5895,7 +6539,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5918,7 +6562,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5941,7 +6585,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5964,7 +6608,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5987,7 +6631,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6010,7 +6654,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -6033,7 +6677,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -6056,7 +6700,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -6079,7 +6723,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -6102,7 +6746,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -6125,7 +6769,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -6148,7 +6792,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -6171,7 +6815,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -6194,7 +6838,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -6217,7 +6861,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -6240,7 +6884,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -6263,7 +6907,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -6286,7 +6930,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -6309,7 +6953,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -6332,7 +6976,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -6355,7 +6999,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -6378,7 +7022,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -6401,7 +7045,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -6424,7 +7068,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -6447,7 +7091,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -6470,7 +7114,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -6493,7 +7137,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -6516,7 +7160,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -6539,7 +7183,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -6562,7 +7206,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -6585,7 +7229,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -6608,7 +7252,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -6631,7 +7275,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -6651,6 +7295,167 @@
         <v>76</v>
       </c>
       <c r="G53" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>74</v>
+      </c>
+      <c r="F54" s="9">
+        <v>76</v>
+      </c>
+      <c r="G54" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>74</v>
+      </c>
+      <c r="F55" s="9">
+        <v>76</v>
+      </c>
+      <c r="G55" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>74</v>
+      </c>
+      <c r="F56" s="9">
+        <v>76</v>
+      </c>
+      <c r="G56" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>74</v>
+      </c>
+      <c r="F57" s="9">
+        <v>76</v>
+      </c>
+      <c r="G57" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>74</v>
+      </c>
+      <c r="F58" s="9">
+        <v>76</v>
+      </c>
+      <c r="G58" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>74</v>
+      </c>
+      <c r="F59" s="9">
+        <v>76</v>
+      </c>
+      <c r="G59" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>74</v>
+      </c>
+      <c r="F60" s="9">
+        <v>76</v>
+      </c>
+      <c r="G60" s="9">
         <v>75</v>
       </c>
     </row>
@@ -6662,19 +7467,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F1A6FD-F375-4FB8-8C30-C4A005067594}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6697,7 +7502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6720,7 +7525,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6743,7 +7548,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6766,7 +7571,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6789,7 +7594,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6812,7 +7617,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6835,7 +7640,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6858,7 +7663,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6881,7 +7686,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6904,7 +7709,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6927,7 +7732,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6950,7 +7755,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6973,7 +7778,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6996,7 +7801,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -7019,7 +7824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -7042,7 +7847,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -7065,7 +7870,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -7088,7 +7893,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -7111,7 +7916,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -7134,7 +7939,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -7157,7 +7962,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -7180,7 +7985,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -7203,7 +8008,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -7226,7 +8031,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -7249,7 +8054,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -7272,7 +8077,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -7295,7 +8100,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -7318,7 +8123,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -7341,7 +8146,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -7364,7 +8169,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -7387,7 +8192,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -7410,7 +8215,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -7433,7 +8238,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -7456,7 +8261,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -7479,7 +8284,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -7502,7 +8307,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -7525,7 +8330,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -7548,7 +8353,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -7571,7 +8376,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -7594,7 +8399,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -7617,7 +8422,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -7640,7 +8445,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -7663,7 +8468,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -7686,7 +8491,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -7709,7 +8514,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -7732,7 +8537,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -7755,7 +8560,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -7778,7 +8583,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -7801,7 +8606,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -7824,7 +8629,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -7847,7 +8652,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -7870,7 +8675,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -7890,6 +8695,167 @@
         <v>117</v>
       </c>
       <c r="G53" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="12">
+        <v>115</v>
+      </c>
+      <c r="F54" s="12">
+        <v>117</v>
+      </c>
+      <c r="G54" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="12">
+        <v>115</v>
+      </c>
+      <c r="F55" s="12">
+        <v>117</v>
+      </c>
+      <c r="G55" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="12">
+        <v>115</v>
+      </c>
+      <c r="F56" s="12">
+        <v>117</v>
+      </c>
+      <c r="G56" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="12">
+        <v>115</v>
+      </c>
+      <c r="F57" s="12">
+        <v>117</v>
+      </c>
+      <c r="G57" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="12">
+        <v>115</v>
+      </c>
+      <c r="F58" s="12">
+        <v>117</v>
+      </c>
+      <c r="G58" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="12">
+        <v>115</v>
+      </c>
+      <c r="F59" s="12">
+        <v>117</v>
+      </c>
+      <c r="G59" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="12">
+        <v>115</v>
+      </c>
+      <c r="F60" s="12">
+        <v>117</v>
+      </c>
+      <c r="G60" s="12">
         <v>116</v>
       </c>
     </row>
@@ -7901,20 +8867,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F720D88E-37F2-4EF2-B2CA-01688ACF7295}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7937,7 +8903,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -7960,7 +8926,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -7983,7 +8949,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -8006,7 +8972,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -8029,7 +8995,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -8052,7 +9018,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -8075,7 +9041,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -8098,7 +9064,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -8121,7 +9087,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -8144,7 +9110,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -8167,7 +9133,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -8190,7 +9156,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -8213,7 +9179,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -8236,7 +9202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -8259,7 +9225,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -8282,7 +9248,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -8305,7 +9271,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -8328,7 +9294,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -8351,7 +9317,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -8374,7 +9340,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -8397,7 +9363,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -8420,7 +9386,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -8443,7 +9409,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -8466,7 +9432,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -8489,7 +9455,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -8512,7 +9478,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -8535,7 +9501,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -8558,7 +9524,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -8581,7 +9547,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -8604,7 +9570,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -8627,7 +9593,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -8650,7 +9616,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -8673,7 +9639,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -8696,7 +9662,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -8719,7 +9685,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -8742,7 +9708,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -8765,7 +9731,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -8788,7 +9754,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -8811,7 +9777,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -8834,7 +9800,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -8857,7 +9823,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -8880,7 +9846,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -8903,7 +9869,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -8926,7 +9892,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -8949,7 +9915,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -8972,7 +9938,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -8995,7 +9961,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -9018,7 +9984,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -9041,7 +10007,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -9064,7 +10030,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -9087,7 +10053,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -9110,7 +10076,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -9130,6 +10096,167 @@
         <v>82</v>
       </c>
       <c r="G53" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>79</v>
+      </c>
+      <c r="F54" s="9">
+        <v>82</v>
+      </c>
+      <c r="G54" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>79</v>
+      </c>
+      <c r="F55" s="9">
+        <v>82</v>
+      </c>
+      <c r="G55" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>79</v>
+      </c>
+      <c r="F56" s="9">
+        <v>82</v>
+      </c>
+      <c r="G56" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>79</v>
+      </c>
+      <c r="F57" s="9">
+        <v>82</v>
+      </c>
+      <c r="G57" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>79</v>
+      </c>
+      <c r="F58" s="9">
+        <v>82</v>
+      </c>
+      <c r="G58" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>79</v>
+      </c>
+      <c r="F59" s="9">
+        <v>82</v>
+      </c>
+      <c r="G59" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>79</v>
+      </c>
+      <c r="F60" s="9">
+        <v>82</v>
+      </c>
+      <c r="G60" s="9">
         <v>80</v>
       </c>
     </row>
@@ -9141,20 +10268,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD5A656-5B30-45CF-B579-A97C69E643A5}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9177,7 +10304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -9200,7 +10327,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -9223,7 +10350,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -9246,7 +10373,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -9269,7 +10396,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -9292,7 +10419,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -9315,7 +10442,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -9338,7 +10465,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -9361,7 +10488,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -9384,7 +10511,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -9407,7 +10534,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -9430,7 +10557,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -9453,7 +10580,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -9476,7 +10603,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -9499,7 +10626,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -9522,7 +10649,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -9545,7 +10672,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -9568,7 +10695,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -9591,7 +10718,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -9614,7 +10741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -9637,7 +10764,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -9660,7 +10787,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -9683,7 +10810,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -9706,7 +10833,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -9729,7 +10856,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -9752,7 +10879,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -9775,7 +10902,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -9798,7 +10925,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -9821,7 +10948,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -9844,7 +10971,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -9867,7 +10994,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -9890,7 +11017,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -9913,7 +11040,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -9936,7 +11063,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -9959,7 +11086,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -9982,7 +11109,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -10005,7 +11132,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -10028,7 +11155,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -10051,7 +11178,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -10074,7 +11201,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -10097,7 +11224,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -10120,7 +11247,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -10143,7 +11270,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -10166,7 +11293,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -10189,7 +11316,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -10212,7 +11339,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -10235,7 +11362,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -10258,7 +11385,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -10281,7 +11408,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -10304,7 +11431,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -10327,7 +11454,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -10350,7 +11477,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -10370,6 +11497,167 @@
         <v>131</v>
       </c>
       <c r="G53" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="14">
+        <v>128</v>
+      </c>
+      <c r="F54" s="14">
+        <v>131</v>
+      </c>
+      <c r="G54" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="14">
+        <v>128</v>
+      </c>
+      <c r="F55" s="14">
+        <v>131</v>
+      </c>
+      <c r="G55" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="14">
+        <v>128</v>
+      </c>
+      <c r="F56" s="14">
+        <v>131</v>
+      </c>
+      <c r="G56" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="14">
+        <v>128</v>
+      </c>
+      <c r="F57" s="14">
+        <v>131</v>
+      </c>
+      <c r="G57" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="14">
+        <v>128</v>
+      </c>
+      <c r="F58" s="14">
+        <v>131</v>
+      </c>
+      <c r="G58" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="14">
+        <v>128</v>
+      </c>
+      <c r="F59" s="14">
+        <v>131</v>
+      </c>
+      <c r="G59" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="14">
+        <v>128</v>
+      </c>
+      <c r="F60" s="14">
+        <v>131</v>
+      </c>
+      <c r="G60" s="14">
         <v>130</v>
       </c>
     </row>
@@ -10381,20 +11669,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3EDF89-A497-4D9B-AE60-D1EDE4F7FB0B}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10417,7 +11705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -10440,7 +11728,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -10463,7 +11751,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -10486,7 +11774,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -10509,7 +11797,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -10532,7 +11820,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -10555,7 +11843,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -10578,7 +11866,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -10601,7 +11889,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -10624,7 +11912,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -10647,7 +11935,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -10670,7 +11958,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -10693,7 +11981,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -10716,7 +12004,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -10739,7 +12027,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -10762,7 +12050,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -10785,7 +12073,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -10808,7 +12096,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -10831,7 +12119,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -10854,7 +12142,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -10877,7 +12165,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -10900,7 +12188,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -10923,7 +12211,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -10946,7 +12234,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -10969,7 +12257,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -10992,7 +12280,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -11015,7 +12303,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -11038,7 +12326,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -11061,7 +12349,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -11084,7 +12372,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -11107,7 +12395,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -11130,7 +12418,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -11153,7 +12441,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -11176,7 +12464,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -11199,7 +12487,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -11222,7 +12510,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -11245,7 +12533,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -11268,7 +12556,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -11291,7 +12579,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -11314,7 +12602,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -11337,7 +12625,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -11360,7 +12648,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -11383,7 +12671,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -11406,7 +12694,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -11429,7 +12717,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -11452,7 +12740,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -11475,7 +12763,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -11498,7 +12786,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -11521,7 +12809,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -11544,7 +12832,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -11567,7 +12855,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -11590,7 +12878,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -11610,6 +12898,167 @@
         <v>254</v>
       </c>
       <c r="G53" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="14">
+        <v>247</v>
+      </c>
+      <c r="F54" s="14">
+        <v>254</v>
+      </c>
+      <c r="G54" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="14">
+        <v>247</v>
+      </c>
+      <c r="F55" s="14">
+        <v>254</v>
+      </c>
+      <c r="G55" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="14">
+        <v>247</v>
+      </c>
+      <c r="F56" s="14">
+        <v>254</v>
+      </c>
+      <c r="G56" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="14">
+        <v>247</v>
+      </c>
+      <c r="F57" s="14">
+        <v>254</v>
+      </c>
+      <c r="G57" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="14">
+        <v>247</v>
+      </c>
+      <c r="F58" s="14">
+        <v>254</v>
+      </c>
+      <c r="G58" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="14">
+        <v>247</v>
+      </c>
+      <c r="F59" s="14">
+        <v>254</v>
+      </c>
+      <c r="G59" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="14">
+        <v>247</v>
+      </c>
+      <c r="F60" s="14">
+        <v>254</v>
+      </c>
+      <c r="G60" s="14">
         <v>250</v>
       </c>
     </row>
